--- a/resources/userdata/amazon_asin_database.xlsx
+++ b/resources/userdata/amazon_asin_database.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9527" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIN 数据库" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,26 +12,181 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ASIN 数据库'!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="22">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +195,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0C0C0"/>
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -52,18 +394,309 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="10"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,7 +1049,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -426,8 +1058,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <cols>
+    <col width="10.1111111111111" customWidth="1" min="1" max="1"/>
+    <col width="11.8888888888889" customWidth="1" min="2" max="2"/>
+    <col width="43.4444444444444" customWidth="1" min="3" max="3"/>
+    <col width="87.2222222222222" customWidth="1" min="4" max="4"/>
+    <col width="65.8888888888889" customWidth="1" min="5" max="5"/>
+    <col width="32.1111111111111" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -461,8 +1101,108 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEYD-568</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B083QH5BK3</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B083QH5BK3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>妻の残業NTRわたし、旦那に嘘をついて残業しています…。 めぐり 溜池ゴロー [DVD]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81RF8kIOYML.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4549831487865</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JUFE-118</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B07YZ92ZJF</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B07YZ92ZJF</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>射精を支配される究極主観JOI 永井マリア Fitch [DVD]</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91QqZTLtsaL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4549831451750</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GVG-907</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B07T2KYJNB</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B07T2KYJNB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>姑の卑猥過ぎる巨乳を狙う娘婿 [DVD]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91X7F-ilfVL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>姑の卑猥過ぎる巨乳を狙う娘婿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="https://www.amazon.co.jp/dp/B083QH5BK3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" display="https://m.media-amazon.com/images/I/81RF8kIOYML.SL1500.jpg" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="https://www.amazon.co.jp/dp/B07YZ92ZJF" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" display="https://m.media-amazon.com/images/I/91QqZTLtsaL.SL1500.jpg" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="https://www.amazon.co.jp/dp/B07T2KYJNB" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" display="https://m.media-amazon.com/images/I/91X7F-ilfVL.SL1500.jpg" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resources/userdata/amazon_asin_database.xlsx
+++ b/resources/userdata/amazon_asin_database.xlsx
@@ -4,13 +4,13 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9527" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIN 数据库" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ASIN 数据库'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ASIN 数据库'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -45,6 +45,21 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -53,6 +68,50 @@
       <name val="宋体"/>
       <charset val="0"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -61,6 +120,43 @@
       <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -74,87 +170,6 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
@@ -165,7 +180,7 @@
       <name val="宋体"/>
       <charset val="0"/>
       <b val="1"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -178,12 +193,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="34">
@@ -195,7 +206,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -207,31 +314,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,25 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,125 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -419,6 +444,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -438,27 +483,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,65 +519,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="00D0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="00D0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="00D0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="00D0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -546,106 +580,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="10"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1058,143 +1108,564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.1111111111111" customWidth="1" min="1" max="1"/>
-    <col width="11.8888888888889" customWidth="1" min="2" max="2"/>
-    <col width="43.4444444444444" customWidth="1" min="3" max="3"/>
-    <col width="87.2222222222222" customWidth="1" min="4" max="4"/>
-    <col width="65.8888888888889" customWidth="1" min="5" max="5"/>
-    <col width="32.1111111111111" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" style="1" min="1" max="1"/>
+    <col width="12" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+    <col width="80" customWidth="1" style="1" min="4" max="4"/>
+    <col width="50" customWidth="1" style="1" min="5" max="5"/>
+    <col width="40" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>影片番号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>ASIN 编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>影片链接</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>商品标题</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>封面 URL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>搜索关键词</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>MEYD-568</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>B083QH5BK3</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B083QH5BK3</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>妻の残業NTRわたし、旦那に嘘をついて残業しています…。 めぐり 溜池ゴロー [DVD]</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/81RF8kIOYML.SL1500.jpg</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>4549831487865</v>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>4549831487865</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>JUFE-118</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>B07YZ92ZJF</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B07YZ92ZJF</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>射精を支配される究極主観JOI 永井マリア Fitch [DVD]</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/91QqZTLtsaL.SL1500.jpg</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>4549831451750</v>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>4549831451750</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>GVG-907</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>B07T2KYJNB</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B07T2KYJNB</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>姑の卑猥過ぎる巨乳を狙う娘婿 [DVD]</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/91X7F-ilfVL.SL1500.jpg</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>姑の卑猥過ぎる巨乳を狙う娘婿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>JUR-600</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>B0GJZL9G8D</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GJZL9G8D</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>全裸椅子取りゲーム、恥辱の中出し輪●―。 マドンナ [DVD]</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/718kUxjDG0L.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>4550566450048</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SSNI-733</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>B084Z94885</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B084Z94885</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>極上の愛人と行くひと晩10発射精する絶倫不倫旅行 橋本ありな エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81fLt8aTWnL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>4549831502247</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SNOS-136</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>B0GPWBSXTH</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GPWBSXTH</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>男女2対2で飲んでエロがってHまでこぎ着けたら…何発ヤっても、まだヤリたい!精子出すの好き好きダブル陽キャビッチ! 七ツ森りり,村上悠華 エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81lQ2d+9wAL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>4550566462003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>SSNI-663</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>B082FD4MFM</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B082FD4MFM</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>中から出てくる白濁汁 マン汁がメレンゲになりダラダラ溢れ出るほどの究極ピストン 坂道みる エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81P4ItKBUmL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>4549831475473</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>IPZZ-795</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>B0GRZW5K2V</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GRZW5K2V</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>昔世話したガキ二人が大層美人になって訪問 喪失感が残る俺を励ます為に汗だくで何度でも何発でも抜いてくれた 佐々木さき,桜乃りの アイデアポケット [DVD]</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81HFdGwSgPL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>4550566470077</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>SNOS-071</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>B0GC5C94KH</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GC5C94KH</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>愛する妻をとことん犯します。喉奥責めイラマ・無理矢理ねじ込みピストン・面汚しブッカケ・吊り下げ拘束 エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71z2zwwPnFL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>4550566433683</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>JUR-636</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>B0GJZBX462</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GJZBX462</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>無防備すぎるノイキャン巨乳人妻 マドンナ [DVD]</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71pMusE8ehL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>4550566450086</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>SSNI-830</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>B08BJ7ZHJB</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B08BJ7ZHJB</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>股下3センチ美脚タイトミニスカナースの誘惑 星宮一花 エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81fGtcEQzFL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>4549831555526</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SSNI-953</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>B08PVW3TS6</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B08PVW3TS6</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>義父の濃厚な舌技で舐め堕ちした美人妻 小島みなみ エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81JfOi+WMlL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>4549831621115</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>FNS-170</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>B0GR7RHLMH</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GR7RHLMH</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>【メーカー特典あり】ラブドールNTR 僕だけの愛玩具は他人のザーメンで白く汚される 浅野心愛（着用済みパンティ＆証明写真）（初回限定）[DVD]</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Vk5OarUbL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>ラブドールNTR 僕だけの愛玩具は他人のザーメンで白く汚される</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>SSNI-992</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>B08TCKH5LM</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B08TCKH5LM</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>憧れの女上司と相部屋がきっかけで・・・ 田舎の宿でこっそ~り何度も射精させられた僕 星宮一花 エスワン ナンバーワンスタイル [DVD]</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81f6Vo2pHfL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>4549831638403</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>SSPD-166</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>B09FLNHG38</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B09FLNHG38</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>バイト先の美女2人を奴隷化ハーレム計画 アタッカーズ [DVD]</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81UhKG8prIL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>4549831727848</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>STARS-171</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>B0B3J3NDT9</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0B3J3NDT9</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>【7日間視聴期限】WドM奴隷 拘束・調教・人体固定 鬼畜大量膣奥出しレ×プ!Special!!!! 本庄鈴 小倉由菜 大量中出し16発!!|オンラインコード版</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81k0gR3tUgL.SL1500.jpg</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>拘束・調教・人体固定 本庄鈴</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="https://www.amazon.co.jp/dp/B083QH5BK3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" display="https://m.media-amazon.com/images/I/81RF8kIOYML.SL1500.jpg" r:id="rId2"/>
@@ -1202,6 +1673,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" display="https://m.media-amazon.com/images/I/91QqZTLtsaL.SL1500.jpg" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="https://www.amazon.co.jp/dp/B07T2KYJNB" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" display="https://m.media-amazon.com/images/I/91X7F-ilfVL.SL1500.jpg" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="https://www.amazon.co.jp/dp/B0GJZL9G8D" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" display="https://m.media-amazon.com/images/I/718kUxjDG0L.SL1500.jpg" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="https://www.amazon.co.jp/dp/B084Z94885" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" display="https://m.media-amazon.com/images/I/81fLt8aTWnL.SL1500.jpg" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="https://www.amazon.co.jp/dp/B0GPWBSXTH" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" display="https://m.media-amazon.com/images/I/81lQ2d+9wAL.SL1500.jpg" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="https://www.amazon.co.jp/dp/B082FD4MFM" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" display="https://m.media-amazon.com/images/I/81P4ItKBUmL.SL1500.jpg" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="https://www.amazon.co.jp/dp/B0GRZW5K2V" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" display="https://m.media-amazon.com/images/I/81HFdGwSgPL.SL1500.jpg" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="https://www.amazon.co.jp/dp/B0GC5C94KH" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" display="https://m.media-amazon.com/images/I/71z2zwwPnFL.SL1500.jpg" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="https://www.amazon.co.jp/dp/B0GJZBX462" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" display="https://m.media-amazon.com/images/I/71pMusE8ehL.SL1500.jpg" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="https://www.amazon.co.jp/dp/B08BJ7ZHJB" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" display="https://m.media-amazon.com/images/I/81fGtcEQzFL.SL1500.jpg" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="https://www.amazon.co.jp/dp/B08PVW3TS6" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" display="https://m.media-amazon.com/images/I/81JfOi+WMlL.SL1500.jpg" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="https://www.amazon.co.jp/dp/B0GR7RHLMH" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" display="https://m.media-amazon.com/images/I/81Vk5OarUbL.SL1500.jpg" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="https://www.amazon.co.jp/dp/B08TCKH5LM" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" display="https://m.media-amazon.com/images/I/81f6Vo2pHfL.SL1500.jpg" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="https://www.amazon.co.jp/dp/B09FLNHG38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" display="https://m.media-amazon.com/images/I/81UhKG8prIL.SL1500.jpg" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="https://www.amazon.co.jp/dp/B0B3J3NDT9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" display="https://m.media-amazon.com/images/I/81k0gR3tUgL.SL1500.jpg" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
